--- a/arquivos/rede-nossa-saude-campos-gerais.xlsx
+++ b/arquivos/rede-nossa-saude-campos-gerais.xlsx
@@ -48,16 +48,16 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="FF0D2A4F"/>
+      <color rgb="FF004159"/>
       <sz val="18"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="FF9A7513"/>
+      <color rgb="FFF07F09"/>
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="FF89909C"/>
+      <color rgb="FF8B8580"/>
       <sz val="10"/>
     </font>
     <font>
@@ -74,12 +74,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="FF0D2A4F"/>
+      <color rgb="FF004159"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="FF0D2A4F"/>
+      <color rgb="FF004159"/>
       <sz val="16"/>
     </font>
     <font>
@@ -89,7 +89,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="FF9A7513"/>
+      <color rgb="FFF07F09"/>
       <sz val="10"/>
     </font>
     <font>
@@ -117,17 +117,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0D2A4F"/>
+        <fgColor rgb="FF004159"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9A7513"/>
+        <fgColor rgb="FFF07F09"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F8FB"/>
+        <fgColor rgb="FFF5F8F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,16 +141,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFE2E6EC"/>
+        <color rgb="FFE3E0DC"/>
       </left>
       <right style="thin">
-        <color rgb="FFE2E6EC"/>
+        <color rgb="FFE3E0DC"/>
       </right>
       <top style="thin">
-        <color rgb="FFE2E6EC"/>
+        <color rgb="FFE3E0DC"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE2E6EC"/>
+        <color rgb="FFE3E0DC"/>
       </bottom>
     </border>
   </borders>
